--- a/data_extactor/batch_10_fa/batch_0068_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0068_fa.xlsx
@@ -508,27 +508,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | مانیتورینگ | گوش دادن فعال | تفکر انتقادی | سخن گفتن | نگارش | یادگیری فعال | ریاضیات</t>
+          <t>درک مطلب | نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن | نگارش | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>حمل و نقل | امور اداری | خدمات مشتریان و پرسنل | مدیریت و سازماندهی | زبان انگلیسی | کامپیوتر و الکترونیک | ایمنی و امنیت عمومی | جغرافیا | پرسنل و منابع انسانی | ریاضیات | مخابرات | اقتصاد و حسابداری | ارتباطات و رسانه | قانون و حکومت | تولید و فرآوری | بازاریابی و فروش</t>
+          <t>حمل و نقل | اداری | خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی | رایانه و الکترونیک | ایمنی و امنیت عمومی | جغرافیا | پرسنل و منابع انسانی | ریاضیات | مخابرات | اقتصاد و حسابداری | ارتباطات و رسانه | قانون و دولت | تولید و فرآوری | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | ترتیب‌دهی به اطلاعات | بینایی نزدیک | حساسیت به مسئله | استدلال قیاسی | بیان کتبی | سرعت ادراکی | انعطاف‌پذیری بستار | سهولت در کار با اعداد | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | وضوح گفتار | سرعت بستار | استدلال ریاضی | تشخیص گفتار | روان بودن ایده‌ها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | ترتیب‌دهی اطلاعات | بینایی نزدیک | حساسیت به مسئله | استدلال قیاسی | بیان کتبی | سرعت ادراکی | انعطاف‌پذیری بستار | توانایی عددی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | وضوح گفتار | سرعت بستار | استدلال ریاضی | تشخیص گفتار | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | فشار زمانی | داخل ساختمان، دارای تهویه مطبوع | ارتباط با دیگران | برخورد با مشتریان خارجی یا عموم مردم | صرف زمان به صورت نشسته | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف مشابه | کار با یا مشارکت در یک گروه کاری یا تیم | موقعیت‌های تعارض | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سطح رقابت | پیامدهای کاری و نتایج سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | مکالمات تلفنی | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای نشستن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | موقعیت‌های تعارض | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سطح رقابت | پیامدهای کاری و نتایج سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>سرپرستان جابجایی بار هواپیما | خریداران و ماموران خرید محصولات کشاورزی | ماموران بار و محموله | پیک‌ها و نامه‌رسان‌ها | کارگزاران گمرک | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | سرپرستان خط اول اپراتورهای ماشین‌آلات جابجایی مواد و وسایل نقلیه | رانندگان کامیونت | متخصصان لجستیک | تحلیل‌گران لجستیک | مهندسان لجستیک | کارمندان خدمات پستی | نامه‌رسان‌های خدمات پستی | کارمندان تدارکات | ماموران خرید به جز محصولات عمده‌فروشی، خرده‌فروشی و کشاورزی | ماموران رزرواسیون، بلیط حمل و نقل و کارمندان سفر | کارمندان ارسال، دریافت و موجودی کالا | بازرسان حمل و نقل | برنامه‌ریزان حمل و نقل | مدیران حمل و نقل، انبارداری و توزیع</t>
+          <t>سرپرستان جابجایی بار هواپیما | خریداران و نمایندگان خرید، محصولات کشاورزی | نمایندگان بار و محموله | پیک‌ها و نامه‌رسان‌ها | کارگزاران گمرک | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | رانندگان کامیون‌های سبک | لجستیسین‌ها | تحلیلگران لجستیک | مهندسان لجستیک | کارمندان خدمات پستی | نامه‌رسان‌های خدمات پستی | کارمندان تدارکات | نمایندگان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | نمایندگان بلیط و رزرواسیون حمل و نقل و کارمندان سفر | کارمندان ارسال، دریافت و موجودی کالا | بازرسان حمل‌ونقل | برنامه‌ریزان حمل‌ونقل | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -570,22 +570,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و پرسنل | حمل و نقل | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | حمل و نقل | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | بینایی دور | تشخیص گفتار | درک کتبی | هماهنگی چند عضو | زبردستی انگشتان | زبردستی دست | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی به اطلاعات | حساسیت به مسئله | بیان کتبی | وضوح گفتار | درک عمق | جهت‌گیری پاسخ | دقت کنترل | ثبات دست و بازو | سرعت ادراکی | استدلال استقرایی | استدلال قیاسی</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | بینایی دور | تشخیص گفتار | درک کتبی | هماهنگی چند عضو | مهارت انگشتان | مهارت دستی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بیان کتبی | وضوح گفتار | درک عمق | جهت‌گیری پاسخ | دقت کنترل | ثبات دست و بازو | سرعت ادراکی | استدلال استقرایی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | آزادی در تصمیم‌گیری | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | ارتباط با دیگران | ایمیل | صرف زمان به صورت نشسته | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | درون وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | داخل ساختمان، دارای تهویه مطبوع | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای انجام حرکات تکراری | خارج از ساختمان، در معرض انواع شرایط آب و هوایی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سلامت و ایمنی سایر کارکنان</t>
+          <t>مکالمات تلفنی | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | ارتباط با دیگران | ایمیل | صرف زمان برای نشستن | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | محیط داخلی، دارای کنترل شرایط محیطی | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای انجام حرکات تکراری | فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سلامت و ایمنی سایر کارکنان</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>سرپرستان جابجایی بار هواپیما | باربران چمدان و پیشخدمت‌های هتل | ماموران بار و محموله | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | رانندگان توزیع و فروش | سرپرستان خط اول اپراتورهای ماشین‌آلات جابجایی مواد و وسایل نقلیه | متصدیان حمل و نقل | رانندگان کامیون‌های سنگین و تریلی | کارگران و جابجا کنندگان دستی بار، انبار و مواد | رانندگان کامیونت | کارمندان پست و اپراتورهای ماشین‌های پستی، به جز خدمات پستی | کارمندان ثبت سفارش | کارمندان خدمات پستی | نامه‌رسان‌های خدمات پستی | دسته‌بندی‌کنندگان، پردازش‌کنندگان و اپراتورهای ماشین‌های پردازش خدمات پستی | لوکوموتیورانان و روسای ایستگاه قطار | کارمندان ارسال، دریافت و موجودی کالا | رانندگان سرویس و شوفرها | انبارداران و جمع‌آوران سفارش | اپراتورهای تلفنخانه، از جمله خدمات پاسخگویی تلفنی</t>
+          <t>سرپرستان جابجایی بار هواپیما | باربران چمدان و پادوهای هتل | نمایندگان بار و محموله | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | رانندگان توزیع و فروشندگان | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | متصدیان حمل و نقل | رانندگان کامیون‌های سنگین و تریلی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | رانندگان کامیون‌های سبک | کارمندان پست و اپراتورهای ماشین‌های پست، به جز اداره پست | کارمندان ثبت سفارش | کارمندان خدمات پستی | نامه‌رسان‌های خدمات پستی | دسته‌بندی‌کنندگان، پردازش‌کنندگان و اپراتورهای ماشین‌های پردازش خدمات پستی | رئیس قطارها و مدیران محوطه راه‌آهن | کارمندان ارسال، دریافت و موجودی کالا | رانندگان شاتل و شوفرها | قفسه‌چین‌ها و پرکننده‌های سفارش | اپراتورهای تلفنخانه، شامل سرویس پاسخگویی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,32 +617,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>پایگاه‌های داده اطلاعات سیستم 911 | نرم‌افزار دیسپچ به کمک کامپیوتر | Corel WordPerfect Office Suite | سیستم‌های سیستم اطلاعات جغرافیایی GIS | Intrado SchoolMessenger | پایگاه‌های داده اطلاعات نیروی انتظامی | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Word | پایگاه داده مرکز ملی اطلاعات جرم (NCIC) | سیستم ملی مخابرات نیروی انتظامی NLETS | نرم‌افزار SAP | Spillman Technologies Spillman Computer-Aided Dispatch | نرم‌افزار مرورگر وب</t>
+          <t>پایگاه‌های داده اطلاعات سیستم 911 | نرم‌افزار اعزام به کمک کامپیوتر | Corel WordPerfect Office Suite | سیستم‌های سیستم اطلاعات جغرافیایی GIS | Intrado SchoolMessenger | پایگاه‌های داده اطلاعات اجرای قانون | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Word | پایگاه داده مرکز ملی اطلاعات جرم (NCIC) | سیستم ملی مخابرات نیروی انتظامی NLETS | نرم‌افزار SAP | Spillman Technologies Spillman Computer-Aided Dispatch | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | یادگیری فعال | مانیتورینگ | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | یادگیری فعال | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | قانون و حکومت | زبان انگلیسی | مخابرات | خدمات مشتریان و پرسنل | جغرافیا | ارتباطات و رسانه | کامپیوتر و الکترونیک | امور اداری | آموزش و پرورش | روانشناسی | پرسنل و منابع انسانی | درمان و مشاوره | مدیریت و سازماندهی</t>
+          <t>ایمنی و امنیت عمومی | قانون و دولت | زبان انگلیسی | مخابرات | خدمات مشتری و شخصی | جغرافیا | ارتباطات و رسانه | رایانه و الکترونیک | اداری | آموزش و پرورش | روان‌شناسی | پرسنل و منابع انسانی | درمان و مشاوره | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | حساسیت به مسئله | تشخیص گفتار | توجه انتخابی | ترتیب‌دهی به اطلاعات | درک کتبی | استدلال قیاسی | استدلال استقرایی | تقسیم توجه | بینایی نزدیک | بیان کتبی | توجه شنیداری | سرعت ادراکی | انعطاف‌پذیری بستار | سرعت بستار | انعطاف‌پذیری دسته‌بندی | روان بودن ایده‌ها</t>
+          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | حساسیت به مسئله | تشخیص گفتار | توجه انتخابی | ترتیب‌دهی اطلاعات | درک کتبی | استدلال قیاسی | استدلال استقرایی | تقسیم توجه | بینایی نزدیک | بیان کتبی | توجه شنیداری | سرعت ادراکی | انعطاف‌پذیری بستار | سرعت بستار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>داخل ساختمان، دارای تهویه مطبوع | مکالمات تلفنی | صرف زمان به صورت نشسته | ارتباط با دیگران | برخورد با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف مشابه | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | ایمیل | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | موقعیت‌های تعارض | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | آزادی در تصمیم‌گیری | فشار زمانی | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامد اشتباه | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارکنان | پیامدهای کاری و نتایج سایر کارکنان | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | نامه‌ها و یادداشت‌های کتبی</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | صرف زمان برای نشستن | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | ایمیل | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | موقعیت‌های تعارض | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | آزادی در تصمیم‌گیری | فشار زمانی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامد خطا | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارکنان | پیامدهای کاری و نتایج سایر کارکنان | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کنترل‌کنندگان ترافیک هوایی | متخصصان عملیات فرودگاه | رانندگان و خدمه آمبولانس، به جز تکنسین‌های فوریت‌های پزشکی | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | مدیران مدیریت بحران | تکنسین‌های فوریت‌های پزشکی | سرپرستان خط اول کارکنان آتش‌نشانی و پیشگیری | سرپرستان خط اول مهمانداران مسافران | سرپرستان خط اول پلیس و کارآگاهان | سرپرستان خط اول کارکنان امنیتی | بازرسان آتش‌نشانی جنگل و متخصصان پیشگیری | پارامدیک‌ها | ماموران گشت پلیس و کلانتر | لوکوموتیورانان و روسای ایستگاه قطار | نگهبانان امنیتی | متخصصان مدیریت امنیت | مدیران امنیت | اپراتورهای تلفنخانه، از جمله خدمات پاسخگویی تلفنی | اپراتورهای تلفن | پلیس ترانزیت و راه‌آهن</t>
+          <t>کنترلرهای ترافیک هوایی | متخصصان عملیات فرودگاه | رانندگان و متصدیان آمبولانس، به جز تکنسین‌های فوریت‌های پزشکی | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | مدیران مدیریت بحران | تکنسین‌های فوریت‌های پزشکی | سرپرستان خط اول آتش‌نشانی و پیشگیری | سرپرستان خط اول مهمانداران مسافری | سرپرستان خط اول پلیس و کارآگاهان | سرپرستان خط اول کارکنان امنیتی | بازرسان و متخصصان پیشگیری از آتش‌سوزی جنگل | پارامدیک‌ها | ماموران گشت پلیس و کلانتر | رئیس قطارها و مدیران محوطه راه‌آهن | نگهبانان امنیتی | متخصصان مدیریت امنیت | مدیران امنیتی | اپراتورهای تلفنخانه، شامل سرویس پاسخگویی | اپراتورهای تلفن | پلیس ترانزیت و راه‌آهن</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,32 +674,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Air-Trak Cloudberry | Bornemann Associates Flight Plan | Command Alkon COMMANDconcrete | نرم‌افزار دیسپچ به کمک کامپیوتر | نرم‌افزار مسیریابی خودکار دیسپچ به کمک کامپیوتر | نرم‌افزار پایگاه داده | Digital Gateway e-automate | Dr. Dispatch | ESRI ArcIMS | نرم‌افزار ایمیل | نرم‌افزار تحلیل طراحی ژئومکانیکی GDA | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | Kronos Workforce Timekeeper | نرم‌افزار توزیع لوکوموتیو | Microsoft Access | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Rail Traffic Track Warrant Control System | نرم‌افزار مدیریت منابع | نرم‌افزار مسیریابی | نرم‌افزار SAP | Sabre travel agent software | نرم‌افزار زمان‌بندی | نرم‌افزار ردیابی منابع موقعیت | TMW PowerSuite | Tangier Sky Scheduler View | نرم‌افزار مدیریت حمل و نقل | نرم‌افزار مرورگر وب</t>
+          <t>Air-Trak Cloudberry | Bornemann Associates Flight Plan | Command Alkon COMMANDconcrete | نرم‌افزار اعزام به کمک کامپیوتر | نرم‌افزار مسیریابی خودکار دیسپچ به کمک کامپیوتر | نرم‌افزار پایگاه داده | Digital Gateway e-automate | Dr. Dispatch | ESRI ArcIMS | نرم‌افزار ایمیل | نرم‌افزار تحلیل طراحی ژئومکانیکی GDA | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | Kronos Workforce Timekeeper | نرم‌افزار توزیع لوکوموتیو | Microsoft Access | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Rail Traffic Track Warrant Control System | نرم‌افزار مدیریت منابع | نرم‌افزار مسیریابی | نرم‌افزار SAP | Sabre travel agent software | نرم‌افزار زمان‌بندی | نرم‌افزار ردیابی منابع موقعیت | TMW PowerSuite | Tangier Sky Scheduler View | نرم‌افزار مدیریت حمل و نقل | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | گوش دادن فعال | مانیتورینگ | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و پرسنل | ایمنی و امنیت عمومی | مدیریت و سازماندهی | امور اداری | زبان انگلیسی | حمل و نقل | پرسنل و منابع انسانی | کامپیوتر و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | ایمنی و امنیت عمومی | مدیریت و اداره | اداری | زبان انگلیسی | حمل و نقل | پرسنل و منابع انسانی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>تشخیص گفتار | وضوح گفتار | درک شفاهی | بیان شفاهی | بینایی نزدیک | استدلال قیاسی | حساسیت به مسئله | درک کتبی | بیان کتبی | توجه انتخابی | ترتیب‌دهی به اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی</t>
+          <t>تشخیص گفتار | وضوح گفتار | درک شفاهی | بیان شفاهی | بینایی نزدیک | استدلال قیاسی | حساسیت به مسئله | درک کتبی | بیان کتبی | توجه انتخابی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | فراوانی تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف مشابه | فشار زمانی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارکنان | صرف زمان به صورت نشسته | نامه‌ها و یادداشت‌های کتبی | برخورد با مشتریان خارجی یا عموم مردم | موقعیت‌های تعارض | صرف زمان برای انجام حرکات تکراری | داخل ساختمان، دارای تهویه مطبوع</t>
+          <t>مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | فراوانی تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف یکسان | فشار زمانی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارکنان | صرف زمان برای نشستن | نامه‌ها و یادداشت‌های کتبی | تعامل با مشتریان خارجی یا عموم مردم | موقعیت‌های تعارض | صرف زمان برای انجام حرکات تکراری | محیط داخلی، دارای کنترل شرایط محیطی</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>سرپرستان جابجایی بار هواپیما | سرپرستان خط اول دستیاران، کارگران و جابجا کنندگان دستی مواد | سرپرستان خط اول اپراتورهای ماشین‌آلات جابجایی مواد و وسایل نقلیه | سرپرستان خط اول تعمیرکاران، نصابان و تکنسین‌های تعمیرات | سرپرستان خط اول کارکنان پشتیبانی اداری و دفتری | سرپرستان خط اول مهمانداران مسافران | رانندگان کامیون‌های سنگین و تریلی | کارگران و جابجا کنندگان دستی بار، انبار و مواد | رانندگان کامیونت | مهندسان لوکوموتیو | روسای پست و مدیران پست | توزیع‌کنندگان و دیسپچرهای برق | کارمندان تولید، برنامه‌ریزی و هماهنگی | اپراتورهای مخابراتی امنیت عمومی | مهندسان محوطه راه‌آهن، اپراتورهای دینکی و هاستلرها | لوکوموتیورانان و روسای ایستگاه قطار | کارمندان ارسال، دریافت و موجودی کالا | رانندگان سرویس و شوفرها | اپراتورهای تلفنخانه، از جمله خدمات پاسخگویی تلفنی | مدیران حمل و نقل, انبارداری و توزیع</t>
+          <t>سرپرستان جابجایی بار هواپیما | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | سرپرستان خط اول مهمانداران مسافری | رانندگان کامیون‌های سنگین و تریلی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | رانندگان کامیون‌های سبک | مهندسان لوکوموتیو | رئیس پست و سرپرستان پست | توزیع‌کنندگان و دیسپچرهای برق | کارمندان تولید، برنامه‌ریزی و هماهنگی | اپراتورهای مخابراتی امنیت عمومی | مهندسان محوطه راه‌آهن، اپراتورهای لکوموتیو مانوری و متصدیان آماده‌سازی لکوموتیو | رئیس قطارها و مدیران محوطه راه‌آهن | کارمندان ارسال، دریافت و موجودی کالا | رانندگان شاتل و شوفرها | اپراتورهای تلفنخانه، شامل سرویس پاسخگویی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -741,22 +741,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و پرسنل | ایمنی و امنیت عمومی | زبان انگلیسی | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | ایمنی و امنیت عمومی | زبان انگلیسی | ریاضیات</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | درک شفاهی | بیان شفاهی | قدرت بالاتنه | سرعت ادراکی | ترتیب‌دهی به اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی دور | انعطاف‌پذیری بدنی | هماهنگی چند عضو | دقت کنترل | ثبات دست و بازو | حساسیت به مسئله | درک کتبی</t>
+          <t>بینایی نزدیک | درک شفاهی | بیان شفاهی | قدرت تنه | سرعت ادراکی | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی دور | انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو | دقت کنترل | ثبات دست و بازو | حساسیت به مسئله | درک کتبی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>خارج از ساختمان، در معرض انواع شرایط آب و هوایی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | درون وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای انجام حرکات تکراری | برخورد با مشتریان خارجی یا عموم مردم | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | فشار زمانی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت تکرار وظایف مشابه | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | صرف زمان برای خم شدن یا پیچاندن بدن | صرف زمان به صورت ایستاده | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | مکالمات تلفنی | ارتباط با دیگران | صرف زمان برای پیاده‌روی یا دویدن | سلامت و ایمنی سایر کارکنان | تاثیر تصمیمات بر همکاران یا نتایج شرکت | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای انجام حرکات تکراری | تعامل با مشتریان خارجی یا عموم مردم | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | فشار زمانی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت تکرار وظایف یکسان | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای ایستادن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | مکالمات تلفنی | ارتباط با دیگران | صرف زمان برای راه رفتن یا دویدن | سلامت و ایمنی سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | نصابان و تعمیرکاران خطوط برق | تکنولوژیست‌ها و تکنسین‌های مهندسی برق و الکترونیک | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تعمیرکاران تجهیزات الکتریکی و الکترونیکی نیروگاه، پست برق و رله | اپراتورهای تاسیسات گاز | تکنسین‌های زمین‌گرمایی | بازرسان، تست‌کنندگان، دسته‌بندی‌کنندگان، نمونه‌برداران و توزین‌کنندگان | کارگران نگهداری و تعمیرات عمومی | لوله‌کش‌ها، نصابان لوله و لوله‌کش‌های بخار | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای نیروگاه | اپراتورهای پمپ، به جز پمپ‌های سرچاهی | سرویس‌کاران سپتیک تانک و پاک‌کنندگان لوله‌های فاضلاب | مهندسان تاسیسات و اپراتورهای دیگ بخار | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب</t>
+          <t>تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | نصابان و تعمیرکاران خطوط انتقال نیروی برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، نیروگاه‌ها، پست‌های برق و رله‌ها | اپراتورهای واحدهای گاز | تکنسین‌های زمین‌گرمایی | بازرسان، آزمایش‌کنندگان، سورترها، نمونه‌برداران و توزین‌کنندگان | کارگران نگهداری و تعمیرات عمومی | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای نیروگاه برق | اپراتورهای پمپ، به جز پمپ‌کنندگان سرچاهی | سرویس‌کاران سپتیک تانک و پاک‌کنندگان لوله‌های فاضلاب | مهندسان تاسیسات و اپراتورهای دیگ بخار | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | درک مطلب | مانیتورینگ | تفکر انتقادی</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و پرسنل | زبان انگلیسی | ریاضیات | بازاریابی و فروش | امور اداری | کامپیوتر و الکترونیک | حمل و نقل</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | فروش و بازاریابی | اداری | رایانه و الکترونیک | حمل و نقل</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | درک کتبی | قدرت بالاتنه | زبردستی دست | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی به اطلاعات | استدلال قیاسی | زبردستی انگشتان | ثبات دست و بازو | توجه انتخابی | سرعت ادراکی | سهولت در کار با اعداد | استدلال ریاضی | استدلال استقرایی | حساسیت به مسئله</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | درک کتبی | قدرت تنه | مهارت دستی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی | مهارت انگشتان | ثبات دست و بازو | توجه انتخابی | سرعت ادراکی | توانایی عددی | استدلال ریاضی | استدلال استقرایی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ارتباط با دیگران | داخل ساختمان، دارای تهویه مطبوع | برخورد با مشتریان خارجی یا عموم مردم | صرف زمان به صورت ایستاده | نزدیکی فیزیکی | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای انجام حرکات تکراری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | اهمیت تکرار وظایف مشابه | مکالمات تلفنی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | تاثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای ایستادن | نزدیکی فیزیکی | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای انجام حرکات تکراری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | اهمیت تکرار وظایف یکسان | مکالمات تلفنی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>کارمندان صدور صورتحساب و ثبت هزینه | ماموران بار و محموله | صندوق‌داران | کارمندان باجه و اجاره کالا | پیک‌ها و نامه‌رسان‌ها | کارمندان بایگانی | متصدیان حمل و نقل | رانندگان کامیونت | کارمندان پست و اپراتورهای ماشین‌های پستی، به جز خدمات پستی | کارمندان دفتری عمومی | کارمندان ثبت سفارش | نامه‌رسان‌های خدمات پستی | دسته‌بندی‌کنندگان، پردازش‌کنندگان و اپراتورهای ماشین‌های پردازش خدمات پستی | روسای پست و مدیران پست | کارمندان تدارکات | کارمندان تولید، برنامه‌ریزی و هماهنگی | کارمندان ارسال، دریافت و موجودی کالا | انبارداران و جمع‌آوران سفارش | اپراتورهای تلفنخانه، از جمله خدمات پاسخگویی تلفنی | تحویل‌داران بانک</t>
+          <t>کارمندان صدور صورتحساب و ثبت | نمایندگان بار و محموله | صندوق‌داران | کارمندان باجه و اجاره | پیک‌ها و نامه‌رسان‌ها | کارمندان بایگانی | متصدیان حمل و نقل | رانندگان کامیون‌های سبک | کارمندان پست و اپراتورهای ماشین‌های پست، به جز اداره پست | کارمندان دفتری عمومی | کارمندان ثبت سفارش | نامه‌رسان‌های خدمات پستی | دسته‌بندی‌کنندگان، پردازش‌کنندگان و اپراتورهای ماشین‌های پردازش خدمات پستی | رئیس پست و سرپرستان پست | کارمندان تدارکات | کارمندان تولید، برنامه‌ریزی و هماهنگی | کارمندان ارسال، دریافت و موجودی کالا | قفسه‌چین‌ها و پرکننده‌های سفارش | اپراتورهای تلفنخانه، شامل سرویس پاسخگویی | تحویل‌داران</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -855,22 +855,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و پرسنل | زبان انگلیسی | ایمنی و امنیت عمومی | بازاریابی و فروش</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ایمنی و امنیت عمومی | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ترتیب‌دهی به اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | قدرت بالاتنه | ثبات دست و بازو | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | درک کتبی | درک شفاهی</t>
+          <t>ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | قدرت تنه | ثبات دست و بازو | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | درک کتبی | درک شفاهی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>خارج از ساختمان، در معرض انواع شرایط آب و هوایی | درون وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | صرف زمان برای انجام حرکات تکراری | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف مشابه | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | داخل ساختمان، دارای تهویه مطبوع | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | برخورد با مشتریان خارجی یا عموم مردم | فراوانی تصمیم‌گیری | ارتباط با دیگران | تاثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | صرف زمان برای انجام حرکات تکراری | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | تعامل با مشتریان خارجی یا عموم مردم | فراوانی تصمیم‌گیری | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>باربران چمدان و پیشخدمت‌های هتل | ماموران بار و محموله | کارمندان باجه و اجاره کالا | پیک‌ها و نامه‌رسان‌ها | کارشناسان خدمات مشتریان | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | رانندگان توزیع و فروش | متصدیان حمل و نقل | رانندگان کامیونت | کارمندان پست و اپراتورهای ماشین‌های پستی، به جز خدمات پستی | کارمندان دفتری عمومی | کارمندان ثبت سفارش | کارمندان خدمات پستی | دسته‌بندی‌کنندگان، پردازش‌کنندگان و اپراتورهای ماشین‌های پردازش خدمات پستی | روسای پست و مدیران پست | ماموران رزرواسیون، بلیط حمل و نقل و کارمندان سفر | کارمندان ارسال، دریافت و موجودی کالا | انبارداران و جمع‌آوران سفارش | اپراتورهای تلفنخانه، از جمله خدمات پاسخگویی تلفنی | مدیران حمل و نقل، انبارداری و توزیع</t>
+          <t>باربران چمدان و پادوهای هتل | نمایندگان بار و محموله | کارمندان باجه و اجاره | پیک‌ها و نامه‌رسان‌ها | نمایندگان خدمات مشتریان | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | رانندگان توزیع و فروشندگان | متصدیان حمل و نقل | رانندگان کامیون‌های سبک | کارمندان پست و اپراتورهای ماشین‌های پست، به جز اداره پست | کارمندان دفتری عمومی | کارمندان ثبت سفارش | کارمندان خدمات پستی | دسته‌بندی‌کنندگان، پردازش‌کنندگان و اپراتورهای ماشین‌های پردازش خدمات پستی | رئیس پست و سرپرستان پست | نمایندگان بلیط و رزرواسیون حمل و نقل و کارمندان سفر | کارمندان ارسال، دریافت و موجودی کالا | قفسه‌چین‌ها و پرکننده‌های سفارش | اپراتورهای تلفنخانه، شامل سرویس پاسخگویی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>مانیتورینگ | تفکر انتقادی | سخن گفتن | درک مطلب</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -917,17 +917,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | زبردستی دست | قدرت ایستا | هماهنگی چند عضو | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی به اطلاعات | درک کتبی | وضوح گفتار | تشخیص گفتار | قدرت بالاتنه | زبردستی انگشتان | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | درک شفاهی</t>
+          <t>بینایی نزدیک | مهارت دستی | قدرت ایستا | هماهنگی چند عضو | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | درک کتبی | وضوح گفتار | تشخیص گفتار | قدرت تنه | مهارت انگشتان | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>داخل ساختمان, دارای تهویه مطبوع | فشار زمانی | صرف زمان برای انجام حرکات تکراری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان به صورت ایستاده | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | سرعت تعیین‌شده توسط سرعت تجهیزات | ارتباط با دیگران | صرف زمان برای پیاده‌روی یا دویدن | میزان اتوماسیون | صرف زمان برای خم شدن یا پیچاندن بدن | اهمیت تکرار وظایف مشابه | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | نزدیکی فیزیکی</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | فشار زمانی | صرف زمان برای انجام حرکات تکراری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای ایستادن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | سرعت تعیین‌شده توسط سرعت تجهیزات | ارتباط با دیگران | صرف زمان برای راه رفتن یا دویدن | میزان خودکارسازی | صرف زمان برای خم کردن یا چرخاندن بدن | اهمیت تکرار وظایف یکسان | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ماموران بار و محموله | اپراتورها و متصدیان نوار نقاله | پیک‌ها و نامه‌رسان‌ها | کاربران ورود داده | کارمندان بایگانی | کارگران و جابجا کنندگان دستی بار، انبار و مواد | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارمندان پست و اپراتورهای ماشین‌های پستی، به جز خدمات پستی | کارمندان دفتری عمومی | اپراتورهای ماشین‌های اداری، به جز کامپیوتر | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندها و لفاف‌پیچ‌های دستی | کارمندان خدمات پستی | نامه‌رسان‌های خدمات پستی | روسای پست و مدیران پست | کارمندان تولید، برنامه‌ریزی و هماهنگی | کارگران بازیافت و احیاء مواد | کارمندان ارسال، دریافت و موجودی کالا | انبارداران و جمع‌آوران سفارش | توزین‌کنندگان، اندازه‌گیران، کنترل‌کنندگان و نمونه‌برداران، ثبت سوابق</t>
+          <t>نمایندگان بار و محموله | اپراتورها و متصدیان نوار نقاله | پیک‌ها و نامه‌رسان‌ها | اپراتورهای ورود داده | کارمندان بایگانی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارمندان پست و اپراتورهای ماشین‌های پست، به جز اداره پست | کارمندان دفتری عمومی | اپراتورهای ماشین‌های اداری، به جز رایانه | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندهای دستی | کارمندان خدمات پستی | نامه‌رسان‌های خدمات پستی | رئیس پست و سرپرستان پست | کارمندان تولید، برنامه‌ریزی و هماهنگی | کارگران بازیافت و احیا | کارمندان ارسال، دریافت و موجودی کالا | قفسه‌چین‌ها و پرکننده‌های سفارش | توزین‌کنندگان، اندازه‌گیران، کنترل‌کنندگان و نمونه‌برداران، ثبت اسناد</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,32 +959,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ABB Production Planning | ADi SmartBOL | Accvision ABMIS | Adobe Acrobat | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Aestiva Purchase Order | Airtable | Applied Software Technologies Asset Maintenance and Materials Management System | Asprova | نرم‌افزار بارنامه | نرم‌افزار بارنامه‌ها | نرم‌افزار برآورد هزینه | Creo Synapse Upfront | DM2 Bills of Lading | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | ERP INDUSTRIOS Material Planning | Enterprise Logix | Epicor Vantage ERP | Exact MAX | Exact Software Macola ES | Factory Edge MRP | FileMaker Pro | نرم‌افزار حسابداری وجوه | Geac MPC Production | Giraffe Production Systems Giraffe Schedule System | Google Docs | Google Drive | Honeywell Wintress PACNet | IBM Notes | Inetsoft | Ingenious ProPlan | Ingenious ProSched | InteProc Material Requirements Planning | Interwave Technology RS Bizware Scheduler | Intuit QuickBooks | KAPES | LSA Visual DBR | LSA Visual Easy Lean | Lamar Info Net | نرم‌افزار MEDITECH | MTI Systems Costimator JS | Made2Manage Supply Chain Management | Maynard PlanStaff Manager | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری فرآیندهای پزشکی | Micro Estimating FabPlan | MicroStrategy Report Services | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics ERP | Microsoft Dynamics GP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | NetSuite ERP | Niku Clarity | Oracle Database | Oracle Flow Manufacturing | Oracle JD Edwards EnterpriseOne | Oracle Manufacturing Scheduling | Oracle PeopleSoft | Oracle Primavera Enterprise Project Portfolio Management | Oracle Primavera Systems | PMC KanbanSIM | PRONTO Xi | نرم‌افزار بهینه‌سازی فرآیند تولید Pelion MPO | Pivotal Z Prestige Scheduler | Preactor APS | Preactor Finite Capacity Scheduling | نرم‌افزار زمان‌بندی و برنامه‌ریزی تولید | QAD Adaptive ERP | Questek Humanis | RSS Solutions NaView | Rytech Software Small Business Inventory Control | SAP Crystal Reports | نرم‌افزار SAP | SYSPRO business software | Sage 300 Construction and Real Estate | Sage MAS 90 ERP | Sage Peachtree Premium Accounting for Manufacturing | Stratford Group INMASS/MRP | زبان پرس‌وجوی ساختاریافته SQL | Waterloo Hydrogeologic TACTIC | Work Technology WorkTech Time | Workbrain Employee Scheduling | Workbrain Time and Attendance | iCode Everest</t>
+          <t>ABB Production Planning | ADi SmartBOL | Accvision ABMIS | Adobe Acrobat | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Aestiva Purchase Order | Airtable | Applied Software Technologies Asset Maintenance and Materials Management System | Asprova | نرم‌افزار بارنامه | نرم‌افزار بارنامه‌ها | نرم‌افزار برآورد هزینه | Creo Synapse Upfront | DM2 Bills of Lading | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | ERP INDUSTRIOS Material Planning | Enterprise Logix | Epicor Vantage ERP | Exact MAX | Exact Software Macola ES | Factory Edge MRP | FileMaker Pro | نرم‌افزار حسابداری صندوق | Geac MPC Production | Giraffe Production Systems Giraffe Schedule System | Google Docs | Google Drive | Honeywell Wintress PACNet | IBM Notes | Inetsoft | Ingenious ProPlan | Ingenious ProSched | InteProc Material Requirements Planning | Interwave Technology RS Bizware Scheduler | Intuit QuickBooks | KAPES | LSA Visual DBR | LSA Visual Easy Lean | Lamar Info Net | نرم‌افزار MEDITECH | MTI Systems Costimator JS | Made2Manage Supply Chain Management | Maynard PlanStaff Manager | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Micro Estimating FabPlan | MicroStrategy Report Services | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics ERP | Microsoft Dynamics GP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | NetSuite ERP | Niku Clarity | Oracle Database | Oracle Flow Manufacturing | Oracle JD Edwards EnterpriseOne | Oracle Manufacturing Scheduling | Oracle PeopleSoft | Oracle Primavera Enterprise Project Portfolio Management | Oracle Primavera Systems | PMC KanbanSIM | PRONTO Xi | نرم‌افزار بهینه‌سازی فرآیند تولید Pelion MPO | Pivotal Z Prestige Scheduler | Preactor APS | Preactor Finite Capacity Scheduling | نرم‌افزار زمان‌بندی و برنامه‌ریزی تولید | QAD Adaptive ERP | Questek Humanis | RSS Solutions NaView | Rytech Software Small Business Inventory Control | SAP Crystal Reports | نرم‌افزار SAP | SYSPRO business software | Sage 300 Construction and Real Estate | Sage MAS 90 ERP | Sage Peachtree Premium Accounting for Manufacturing | Stratford Group INMASS/MRP | زبان پرس‌وجوی ساختاریافته SQL | Waterloo Hydrogeologic TACTIC | Work Technology WorkTech Time | Workbrain Employee Scheduling | Workbrain Time and Attendance | iCode Everest</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | گوش دادن فعال | تفکر انتقادی | نگارش | مانیتورینگ</t>
+          <t>درک مطلب | سخن گفتن | گوش دادن فعال | تفکر انتقادی | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | خدمات مشتریان و پرسنل | زبان انگلیسی | امور اداری | مدیریت و سازماندهی | کامپیوتر و الکترونیک</t>
+          <t>تولید و فرآوری | خدمات مشتری و شخصی | زبان انگلیسی | اداری | مدیریت و اداره | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | ترتیب‌دهی به اطلاعات | بیان شفاهی | حساسیت به مسئله | درک کتبی | بینایی نزدیک | بیان کتبی | استدلال قیاسی | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | سرعت ادراکی | استدلال استقرایی</t>
+          <t>درک شفاهی | ترتیب‌دهی اطلاعات | بیان شفاهی | حساسیت به مسئله | درک کتبی | بینایی نزدیک | بیان کتبی | استدلال قیاسی | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | سرعت ادراکی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | فشار زمانی | ایمیل | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | داخل ساختمان، دارای تهویه مطبوع | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فراوانی تصمیم‌گیری | صرف زمان به صورت نشسته | تاثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | فشار زمانی | ایمیل | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فراوانی تصمیم‌گیری | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | سرپرستان خط اول دستیاران، کارگران و جابجا کنندگان دستی مواد | سرپرستان خط اول اپراتورهای ماشین‌آلات جابجایی مواد و وسایل نقلیه | سرپرستان خط اول تعمیرکاران، نصابان و تکنسین‌های تعمیرات | سرپرستان خط اول کارکنان پشتیبانی اداری و دفتری | سرپرستان خط اول کارگران تولید و عملیاتی | تکنولوژیست‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مدیران تولید صنعتی | کارگران و جابجا کنندگان دستی بار، انبار و مواد | متخصصان لجستیک | تحلیل‌گران لجستیک | کارمندان تدارکات | متخصصان مدیریت پروژه | کارمندان ارسال، دریافت و موجودی کالا | انبارداران و جمع‌آوران سفارش | مدیران زنجیره تامین | مونتاژکنندگان تیمی | مدیران حمل و نقل، انبارداری و توزیع | توزین‌کنندگان، اندازه‌گیران، کنترل‌کنندگان و نمونه‌برداران، ثبت سوابق</t>
+          <t>دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | سرپرستان رده اول کارگران تولید و بهره‌برداری | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مدیران تولید صنعتی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | لجستیسین‌ها | تحلیلگران لجستیک | کارمندان تدارکات | متخصصان مدیریت پروژه | کارمندان ارسال، دریافت و موجودی کالا | قفسه‌چین‌ها و پرکننده‌های سفارش | مدیران زنجیره تأمین | مونتاژکاران تیمی | مدیران حمل‌ونقل، انبارداری و توزیع | توزین‌کنندگان، اندازه‌گیران، کنترل‌کنندگان و نمونه‌برداران، ثبت اسناد</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | گوش دادن فعال | مانیتورینگ | تفکر انتقادی</t>
+          <t>سخن گفتن | درک مطلب | گوش دادن فعال | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>امور اداری | کامپیوتر و الکترونیک | تولید و فرآوری | ریاضیات | زبان انگلیسی</t>
+          <t>اداری | رایانه و الکترونیک | تولید و فرآوری | ریاضیات | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی به اطلاعات | درک شفاهی | ثبات دست و بازو | وضوح گفتار | تشخیص گفتار | زبردستی دست | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | بیان کتبی | درک کتبی</t>
+          <t>بینایی نزدیک | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | درک شفاهی | ثبات دست و بازو | وضوح گفتار | تشخیص گفتار | مهارت دستی | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | بیان کتبی | درک کتبی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | فشار زمانی | داخل ساختمان، بدون تهویه مطبوع | ارتباط با دیگران | مکالمات تلفنی | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف مشابه | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | برخورد با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | فشار زمانی | محیط داخلی، بدون کنترل شرایط محیطی | ارتباط با دیگران | مکالمات تلفنی | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ماموران بار و محموله | پیک‌ها و نامه‌رسان‌ها | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | متصدیان حمل و نقل | کارگران و جابجا کنندگان دستی بار، انبار و مواد | تحلیل‌گران لجستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارمندان پست و اپراتورهای ماشین‌های پستی، به جز خدمات پستی | کارمندان ثبت سفارش | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندها و لفاف‌پیچ‌های دستی | کارمندان خدمات پستی | نامه‌رسان‌های خدمات پستی | دسته‌بندی‌کنندگان، پردازش‌کنندگان و اپراتورهای ماشین‌های پردازش خدمات پستی | کارمندان تدارکات | کارمندان تولید، برنامه‌ریزی و هماهنگی | انبارداران و جمع‌آوران سفارش | بارگیران واگن مخزنی، کامیون و کشتی | مدیران حمل و نقل، انبارداری و توزیع | توزین‌کنندگان، اندازه‌گیران، کنترل‌کنندگان و نمونه‌برداران، ثبت سوابق</t>
+          <t>نمایندگان بار و محموله | پیک‌ها و نامه‌رسان‌ها | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | متصدیان حمل و نقل | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | تحلیلگران لجستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارمندان پست و اپراتورهای ماشین‌های پست، به جز اداره پست | کارمندان ثبت سفارش | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندهای دستی | کارمندان خدمات پستی | نامه‌رسان‌های خدمات پستی | دسته‌بندی‌کنندگان، پردازش‌کنندگان و اپراتورهای ماشین‌های پردازش خدمات پستی | کارمندان تدارکات | کارمندان تولید، برنامه‌ریزی و هماهنگی | قفسه‌چین‌ها و پرکننده‌های سفارش | بارگیران واگن مخزنی، کامیون و کشتی | مدیران حمل‌ونقل، انبارداری و توزیع | توزین‌کنندگان، اندازه‌گیران، کنترل‌کنندگان و نمونه‌برداران، ثبت اسناد</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0068_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0068_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | نظارت | شنیدن فعال | تفکر انتقادی | سخن گفتن | نگارش | یادگیری فعال | ریاضیات</t>
+          <t>درک مطلب | نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن | نگارش | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | امور اداری و دفتری | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | زبان انگلیسی | رایانه و الکترونیک | ایمنی و امنیت عمومی | جغرافیا | پرسنلی و منابع انسانی | ریاضیات | مخابرات و ارتباطات دوربرد | اقتصاد و حسابداری | ارتباطات و رسانه | حقوق و مقررات دولتی | تولید و فراوری | فروش و بازاریابی</t>
+          <t>حمل و نقل | اداری | خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی | رایانه و الکترونیک | ایمنی و امنیت عمومی | جغرافیا | پرسنل و منابع انسانی | ریاضیات | مخابرات | اقتصاد و حسابداری | ارتباطات و رسانه | قانون و دولت | تولید و فرآوری | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | مرتب‌سازی اطلاعات | دید نزدیک | حساسیت به مسئله | استدلال قیاسی | بیان کتبی | سرعت ادراک | انعطاف‌پذیری بستن الگو | کار با اعداد | انعطاف‌پذیری در طبقه‌بندی | استدلال استقرایی | وضوح گفتار | سرعت در درک الگوها | استدلال ریاضی | تشخیص گفتار | روانی و سیالی ایده‌ها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | ترتیب‌دهی اطلاعات | بینایی نزدیک | حساسیت به مسئله | استدلال قیاسی | بیان کتبی | سرعت ادراکی | انعطاف‌پذیری بستار | توانایی عددی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | وضوح گفتار | سرعت بستار | استدلال ریاضی | تشخیص گفتار | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>سرپرستان باربری و تخلیه و بارگیری هوایی | خریداران و مأموران خرید محصولات کشاورزی | متصدیان باربری و حمل‌ونقل کالا | نامه‌رسان‌ها و پیک‌ها | کارگزاران گمرکی (حق‌العمل‌کاران گمرک) | متصدیان دیسپاچ و اعزام (به‌جز پلیس، آتش‌نشانی و اورژانس) | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی مواد | رانندگان کامیونت و وانت‌بار | کارشناسان لجستیک | تحلیل‌گران لجستیک | مهندسان لجستیک | متصدیان باجه پست | نامه‌رسان‌های پست | کارمندان امور تدارکات و خرید | مأموران خرید (به‌جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی) | متصدیان صدور بلیط و پذیرش مسافر و کارمندان آژانس‌های مسافرتی | کارمندان ارسال، دریافت و انبارداری | بازرسان حمل‌ونقل | برنامه‌ریزان حمل‌ونقل | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>سرپرستان بارگیری و جابه‌جایی بار هواپیما | خریداران و کارشناسان خرید محصولات کشاورزی | کارگزاران حمل‌ونقل و بار | پیک‌ها و نامه‌رسان‌ها | حق‌العمل‌کاران و کارگزاران گمرکی | متصدیان دیسپاچ و اعزام | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | رانندگان خودروهای باربری سبک و وانت‌بارها | کارشناسان لجستیک و مدیریت زنجیره تأمین | تحلیل‌گران لجستیک و فرایند توزیع | مهندسان لجستیک و زنجیره تأمین | متصدیان باجه و امور پستی | نامه‌رسان‌ها و موزعین پست | کارمندان تدارکات و کارپردازی | کارشناسان خرید و امور قراردادها | متصدیان فروش بلیت، رزرواسیون و خدمات سفر | کارمندان انبار، ارسال و دریافت کالا | بازرسان ترابری و حمل‌ونقل | برنامه‌ریزان سیستم‌های حمل‌ونقل | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,22 +560,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>نرم‌افزار Microsoft Excel | نرم‌افزار Microsoft Office | نرم‌افزار Microsoft Outlook | نرم‌افزار Microsoft Word | نرم‌افزارهای مسیریابی و نقشه‌خوانی</t>
+          <t>نرم‌افزار Microsoft Excel | نرم‌افزار Microsoft Office | نرم‌افزار Microsoft Outlook | نرم‌افزار Microsoft Word | نرم‌افزار نقشه‌برداری مسیر</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | تفکر انتقادی | نگارش | درک مطلب</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | حمل‌ونقل | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | حمل و نقل | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | دید دور | تشخیص گفتار | درک کتبی | هماهنگی چند عضو بدن | چابکی انگشتان | چابکی دستی | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | حساسیت به مسئله | بیان کتبی | وضوح گفتار | درک عمق | جهت‌یابی پاسخ | دقت کنترل حرکتی | ثبات دست و بازو | سرعت ادراک | استدلال استقرایی | استدلال قیاسی</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | بینایی دور | تشخیص گفتار | درک کتبی | هماهنگی چند عضو | مهارت انگشتان | مهارت دستی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بیان کتبی | وضوح گفتار | درک عمق | جهت‌گیری پاسخ | دقت کنترل | ثبات دست و بازو | سرعت ادراکی | استدلال استقرایی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>سرپرستان باربری و تخلیه و بارگیری هوایی | متصدیان حمل بار مسافران و باربرها | متصدیان باربری و حمل‌ونقل کالا | متصدیان دیسپاچ و اعزام (به‌جز پلیس، آتش‌نشانی و اورژانس) | رانندگان توزیع و ویزیتورها | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی مواد | کارشناسان و متصدیان فورواردری و حمل‌ونقل بین‌المللی کالا | رانندگان کامیون سنگین و تریلی | کارگران جابه‌جایی دستی بار و اثاثیه | رانندگان کامیونت و وانت‌بار | کارمندان پستی و اپراتورهای ماشین‌های تمبر و بسته‌بندی اداری | کارمندان ثبت سفارشات | متصدیان باجه پست | نامه‌رسان‌های پست | تفکیک‌کنندگان، پردازش‌گران و اپراتورهای دستگاه‌های مرتب‌سازی پست | روسای قطار و مدیران ایستگاه راه‌آهن | کارمندان ارسال، دریافت و انبارداری | رانندگان سرویس و تشریفات | چیدمان‌کنندگان قفسه و آماده‌کنندگان سفارشات | متصدیان تلفنخانه و مراکز پاسخگویی</t>
+          <t>سرپرستان بارگیری و جابه‌جایی بار هواپیما | متصدیان حمل بار و خدمات هتل | کارگزاران حمل‌ونقل و بار | متصدیان دیسپاچ و اعزام | رانندگان توزیع و فروش مویرگی | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | کارشناسان و متصدیان فورواردری و حمل‌ونقل بین‌المللی کالا | رانندگان خودروهای سنگین و کشنده‌ها | کارگران جابه‌جایی دستی بار، کالا و مصالح | رانندگان خودروهای باربری سبک و وانت‌بارها | کارمندان امور مراسلات و متصدیان ماشین‌های پستی، به جز پست دولتی | متصدیان ثبت و پیگیری سفارش‌ها | متصدیان باجه و امور پستی | نامه‌رسان‌ها و موزعین پست | اپراتورها و متصدیان تفکیک و پردازش پستی | رؤسای قطار و مدیران محوطه راه‌آهن | کارمندان انبار، ارسال و دریافت کالا | رانندگان خودروهای سرویس و تشریفات | متصدیان چیدمان و آماده‌سازی سفارش | اپراتورهای مراکز تلفن و پاسخگویی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | یادگیری فعال | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | یادگیری فعال | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | حقوق و مقررات دولتی | زبان انگلیسی | مخابرات و ارتباطات دوربرد | خدمات مشتریان و خدمات فردی | جغرافیا | ارتباطات و رسانه | رایانه و الکترونیک | امور اداری و دفتری | آموزش و تدریس | روان‌شناسی | پرسنلی و منابع انسانی | درمان و مشاوره‌گری | مدیریت و امور اداری</t>
+          <t>ایمنی و امنیت عمومی | قانون و دولت | زبان انگلیسی | مخابرات | خدمات مشتری و شخصی | جغرافیا | ارتباطات و رسانه | رایانه و الکترونیک | اداری | آموزش و پرورش | روان‌شناسی | پرسنل و منابع انسانی | درمان و مشاوره | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | حساسیت به مسئله | تشخیص گفتار | توجه انتخابی | مرتب‌سازی اطلاعات | درک کتبی | استدلال قیاسی | استدلال استقرایی | تقسیم زمان و توجه | دید نزدیک | بیان کتبی | تمرکز و توجه شنیداری | سرعت ادراک | انعطاف‌پذیری بستن الگو | سرعت در درک الگوها | انعطاف‌پذیری در طبقه‌بندی | روانی و سیالی ایده‌ها</t>
+          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | حساسیت به مسئله | تشخیص گفتار | توجه انتخابی | ترتیب‌دهی اطلاعات | درک کتبی | استدلال قیاسی | استدلال استقرایی | تقسیم توجه | بینایی نزدیک | بیان کتبی | توجه شنیداری | سرعت ادراکی | انعطاف‌پذیری بستار | سرعت بستار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کنترل‌کنندگان ترافیک هوایی | کارشناسان عملیات فرودگاهی | رانندگان و خدمه آمبولانس (به‌جز تکنسین‌های فوریت‌های پزشکی) | متصدیان دیسپاچ و اعزام (به‌جز پلیس، آتش‌نشانی و اورژانس) | مدیران مدیریت بحران و پدافند غیرعامل | تکنسین‌های فوریت‌های پزشکی | سرپرستان رده‌اول آتش‌نشانی و پیشگیری از حریق | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده‌اول پلیس و کارآگاهان | سرپرستان رده‌اول مأموران حراست و نگهبانی | بازرسان و کارشناسان پیشگیری از آتش‌سوزی جنگل‌ها | کارشناسان فوریت‌های پزشکی (پارامدیک) | افسران گشت پلیس | روسای قطار و مدیران ایستگاه راه‌آهن | مأموران حراست و نگهبانان | کارشناسان مدیریت حفاظت و امنیت | مدیران حراست و حفاظت فیزیکی | متصدیان تلفنخانه و مراکز پاسخگویی | اپراتورهای تلفن | مأموران پلیس راه‌آهن و مترو</t>
+          <t>کنترلرهای ترافیک هوایی | کارشناسان عملیات فرودگاهی | رانندگان و خدمه آمبولانس، به‌جز تکنسین‌های فوریت‌های پزشکی | متصدیان دیسپاچ و اعزام | مدیران مدیریت بحران و پدافند غیرعامل | تکنسین‌های فوریت‌های پزشکی | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده‌اول پلیس و کارآگاهان | سرپرستان رده‌اول کارکنان حراست و انتظامات | بازرسان و کارشناسان پیشگیری از حریق جنگل | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | ماموران گشت پلیس و کلانتری | رؤسای قطار و مدیران محوطه راه‌آهن | نگهبانان و ماموران حراست | کارشناسان مدیریت حراست و امنیت فیزیکی | مدیران حراست و انتظامات | اپراتورهای مراکز تلفن و پاسخگویی | اپراتورهای تلفن | پلیس ترانزیت و راه‌آهن</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | نظارت | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | مدیریت و امور اداری | امور اداری و دفتری | زبان انگلیسی | حمل‌ونقل | پرسنلی و منابع انسانی | رایانه و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | ایمنی و امنیت عمومی | مدیریت و اداره | اداری | زبان انگلیسی | حمل و نقل | پرسنل و منابع انسانی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>تشخیص گفتار | وضوح گفتار | درک شفاهی | بیان شفاهی | دید نزدیک | استدلال قیاسی | حساسیت به مسئله | درک کتبی | بیان کتبی | توجه انتخابی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | استدلال استقرایی</t>
+          <t>تشخیص گفتار | وضوح گفتار | درک شفاهی | بیان شفاهی | بینایی نزدیک | استدلال قیاسی | حساسیت به مسئله | درک کتبی | بیان کتبی | توجه انتخابی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>سرپرستان باربری و تخلیه و بارگیری هوایی | سرپرستان رده‌اول کارگران خدماتی و جابه‌جایی دستی مواد | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی مواد | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول کارکنان اداری و پشتیبانی دفتری | سرپرستان رده‌اول مهمانداران و خدمه مسافری | رانندگان کامیون سنگین و تریلی | کارگران جابه‌جایی دستی بار و اثاثیه | رانندگان کامیونت و وانت‌بار | لکوموتیورانان | مدیران و روسای ادارات پست | متصدیان توزیع و دیسپاچینگ شبکه برق | کارمندان برنامه‌ریزی، تولید و پیگیری امور | اپراتورهای فوریت‌های پلیسی و امدادی | مهندسان مانور راه‌آهن و لکوموتیورانان جابه‌جایی واگن | روسای قطار و مدیران ایستگاه راه‌آهن | کارمندان ارسال، دریافت و انبارداری | رانندگان سرویس و تشریفات | متصدیان تلفنخانه و مراکز پاسخگویی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>سرپرستان بارگیری و جابه‌جایی بار هواپیما | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول مهمانداران و خدمه مسافری | رانندگان خودروهای سنگین و کشنده‌ها | کارگران جابه‌جایی دستی بار، کالا و مصالح | رانندگان خودروهای باربری سبک و وانت‌بارها | لکوموتیورانان | مدیران و رؤسای دفاتر پستی | دیسپچرها و توزیع‌کنندگان شبکه برق | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | اپراتورهای فوریت‌های پلیسی و امدادی | لکوموتیورانان محوطه راه‌آهن و رانندگان لکوموتیوهای کوچک مانوری | رؤسای قطار و مدیران محوطه راه‌آهن | کارمندان انبار، ارسال و دریافت کالا | رانندگان خودروهای سرویس و تشریفات | اپراتورهای مراکز تلفن و پاسخگویی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | زبان انگلیسی | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | ایمنی و امنیت عمومی | زبان انگلیسی | ریاضیات</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | بیان شفاهی | قدرت عضلانی تنه | سرعت ادراک | مرتب‌سازی اطلاعات | وضوح گفتار | تشخیص گفتار | دید دور | انعطاف‌پذیری بالاتنه | هماهنگی چند عضو بدن | دقت کنترل حرکتی | ثبات دست و بازو | حساسیت به مسئله | درک کتبی</t>
+          <t>بینایی نزدیک | درک شفاهی | بیان شفاهی | قدرت تنه | سرعت ادراکی | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی دور | انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو | دقت کنترل | ثبات دست و بازو | حساسیت به مسئله | درک کتبی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان کالیبراسیون | نصابان و تعمیرکاران کنترل‌کننده‌ها و شیرآلات صنعتی (به‌جز درب‌های مکانیکی) | تعمیرکاران الکتروموتورها، ابزارهای برقی و تجهیزات وابسته | نصابان و تعمیرکاران خطوط انتقال و توزیع برق | کاردان‌ها و تکنسین‌های مهندسی برق و الکترونیک | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی ناوگان حمل‌ونقل | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تعمیرکاران تجهیزات الکتریکی نیروگاه‌ها، پست‌ها و رله‌های حفاظتی | اپراتورهای پالایشگاه و ایستگاه‌های تقویت فشار گاز | تکنسین‌های انرژی زمین‌گرمایی | بازرسان، آزمون‌گران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | کارگران تعمیرات و نگهداری عمومی | لوله‌کش‌ها و نصابان لوله‌های تاسیساتی و بخار | متصدیان توزیع و دیسپاچینگ شبکه برق | اپراتورهای نیروگاه‌های برق | اپراتورهای پمپ‌ها و ایستگاه‌های پمپاژ (به‌جز پمپ‌های سرچاهی) | سرویس‌کاران مخازن سپتیک و لایروب‌های خطوط فاضلاب | مهندسان موتورخانه و اپراتورهای دیگ‌های بخار صنعتی | نصابان و تعمیرکاران تجهیزات مخابراتی (به‌جز خطوط شبکه) | اپراتورهای تصفیه‌خانه‌ها و شبکه‌های آب و فاضلاب</t>
+          <t>تکنسین‌ها و کارشناسان فنی کالیبراسیون | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | تکنسین‌ها و سیم‌بانان خطوط انتقال و توزیع برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | اپراتورهای تأسیسات و پالایشگاه‌های گاز | تکنسین‌های سامانه‌های زمین‌گرمایی | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | کارگران عمومی تعمیرات و نگهداری تاسیسات | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | دیسپچرها و توزیع‌کنندگان شبکه برق | اپراتورهای نیروگاه برق | اپراتورهای پمپ، به‌جز پمپ‌های سرچاهی | سرویس‌کاران مخازن سپتیک و لایروبان مجاری فاضلاب | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نظارت | تفکر انتقادی</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | ریاضیات | فروش و بازاریابی | امور اداری و دفتری | رایانه و الکترونیک | حمل‌ونقل</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | فروش و بازاریابی | اداری | رایانه و الکترونیک | حمل و نقل</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | وضوح گفتار | تشخیص گفتار | درک کتبی | قدرت عضلانی تنه | چابکی دستی | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | استدلال قیاسی | چابکی انگشتان | ثبات دست و بازو | توجه انتخابی | سرعت ادراک | کار با اعداد | استدلال ریاضی | استدلال استقرایی | حساسیت به مسئله</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | درک کتبی | قدرت تنه | مهارت دستی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی | مهارت انگشتان | ثبات دست و بازو | توجه انتخابی | سرعت ادراکی | توانایی عددی | استدلال ریاضی | استدلال استقرایی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>کارمندان صدور صورت‌حساب و قبوض | متصدیان باربری و حمل‌ونقل کالا | صندوق‌داران | متصدیان باجه کرایه و اجاره کالا | نامه‌رسان‌ها و پیک‌ها | کارمندان بایگانی | کارشناسان و متصدیان فورواردری و حمل‌ونقل بین‌المللی کالا | رانندگان کامیونت و وانت‌بار | کارمندان پستی و اپراتورهای ماشین‌های تمبر و بسته‌بندی اداری | کارمندان امور دفتری عمومی | کارمندان ثبت سفارشات | نامه‌رسان‌های پست | تفکیک‌کنندگان، پردازش‌گران و اپراتورهای دستگاه‌های مرتب‌سازی پست | روسای دفاتر و ادارات پست | کارمندان امور تدارکات و خرید | کارمندان برنامه‌ریزی، تولید و پیگیری امور | کارمندان ارسال، دریافت و انبارداری | چیدمان‌کنندگان قفسه و آماده‌کنندگان سفارشات | متصدیان تلفنخانه و مراکز پاسخگویی | تحویل‌داران بانکی</t>
+          <t>کارمندان صدور صورتحساب و ثبت اسناد مالی | کارگزاران حمل‌ونقل و بار | صندوق‌داران | متصدیان باجه و کرایه کالا و خدمات | پیک‌ها و نامه‌رسان‌ها | متصدیان بایگانی و اسناد | کارشناسان و متصدیان فورواردری و حمل‌ونقل بین‌المللی کالا | رانندگان خودروهای باربری سبک و وانت‌بارها | کارمندان امور مراسلات و متصدیان ماشین‌های پستی، به جز پست دولتی | متصدیان امور دفتری و امور عمومی اداری | متصدیان ثبت و پیگیری سفارش‌ها | نامه‌رسان‌ها و موزعین پست | اپراتورها و متصدیان تفکیک و پردازش پستی | مدیران و رؤسای دفاتر پستی | کارمندان تدارکات و کارپردازی | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | کارمندان انبار، ارسال و دریافت کالا | متصدیان چیدمان و آماده‌سازی سفارش | اپراتورهای مراکز تلفن و پاسخگویی | تحویل‌داران و متصدیان امور بانکی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | ایمنی و امنیت عمومی | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ایمنی و امنیت عمومی | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>مرتب‌سازی اطلاعات | دید نزدیک | وضوح گفتار | تشخیص گفتار | قدرت عضلانی تنه | ثبات دست و بازو | انعطاف‌پذیری در طبقه‌بندی | حساسیت به مسئله | درک کتبی | درک شفاهی</t>
+          <t>ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | قدرت تنه | ثبات دست و بازو | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | درک کتبی | درک شفاهی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>متصدیان حمل بار مسافران و باربرها | متصدیان باربری و حمل‌ونقل کالا | متصدیان باجه کرایه و اجاره کالا | نامه‌رسان‌ها و پیک‌ها | کارشناسان خدمات مشتریان | متصدیان دیسپاچ و اعزام (به‌جز پلیس، آتش‌نشانی و اورژانس) | رانندگان توزیع و ویزیتورها | کارشناسان و متصدیان فورواردری و حمل‌ونقل بین‌المللی کالا | رانندگان کامیونت و وانت‌بار | کارمندان پستی و اپراتورهای ماشین‌های تمبر و بسته‌بندی اداری | کارمندان امور دفتری عمومی | کارمندان ثبت سفارشات | متصدیان باجه پست | تفکیک‌کنندگان، پردازش‌گران و اپراتورهای دستگاه‌های مرتب‌سازی پست | روسای دفاتر و ادارات پست | متصدیان صدور بلیط و پذیرش مسافر و کارمندان آژانس‌های مسافرتی | کارمندان ارسال، دریافت و انبارداری | چیدمان‌کنندگان قفسه و آماده‌کنندگان سفارشات | متصدیان تلفنخانه و مراکز پاسخگویی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>متصدیان حمل بار و خدمات هتل | کارگزاران حمل‌ونقل و بار | متصدیان باجه و کرایه کالا و خدمات | پیک‌ها و نامه‌رسان‌ها | کارشناسان خدمات و پشتیبانی مشتریان | متصدیان دیسپاچ و اعزام | رانندگان توزیع و فروش مویرگی | کارشناسان و متصدیان فورواردری و حمل‌ونقل بین‌المللی کالا | رانندگان خودروهای باربری سبک و وانت‌بارها | کارمندان امور مراسلات و متصدیان ماشین‌های پستی، به جز پست دولتی | متصدیان امور دفتری و امور عمومی اداری | متصدیان ثبت و پیگیری سفارش‌ها | متصدیان باجه و امور پستی | اپراتورها و متصدیان تفکیک و پردازش پستی | مدیران و رؤسای دفاتر پستی | متصدیان فروش بلیت، رزرواسیون و خدمات سفر | کارمندان انبار، ارسال و دریافت کالا | متصدیان چیدمان و آماده‌سازی سفارش | اپراتورهای مراکز تلفن و پاسخگویی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | چابکی دستی | توانایی و استقامت بدنی | هماهنگی چند عضو بدن | سرعت ادراک | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | درک کتبی | وضوح گفتار | تشخیص گفتار | قدرت عضلانی تنه | چابکی انگشتان | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | درک شفاهی</t>
+          <t>بینایی نزدیک | مهارت دستی | قدرت ایستا | هماهنگی چند عضو | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | درک کتبی | وضوح گفتار | تشخیص گفتار | قدرت تنه | مهارت انگشتان | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>متصدیان باربری و حمل‌ونقل کالا | اپراتورها و مراقبان نوار نقاله | نامه‌رسان‌ها و پیک‌ها | متصدیان ورود اطلاعات (داده‌آمایان) | کارمندان بایگانی | کارگران جابه‌جایی دستی بار و اثاثیه | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات تولیدی | کارمندان پستی و اپراتورهای ماشین‌های تمبر و بسته‌بندی اداری | کارمندان امور دفتری عمومی | اپراتورهای ماشین‌های اداری (به‌جز رایانه) | اپراتورها و مراقبان ماشین‌های بسته‌بندی و پرکن | کارگران بسته‌بندی دستی | متصدیان باجه پست | نامه‌رسان‌های پست | روسای دفاتر و ادارات پست | کارمندان برنامه‌ریزی، تولید و پیگیری امور | کارگران بازیافت و تفکیک ضایعات | کارمندان ارسال، دریافت و انبارداری | چیدمان‌کنندگان قفسه و آماده‌کنندگان سفارشات | توزین‌گران، اندازه‌گیران، کنترل‌کنندگان و نمونه‌برداران ثبت سوابق</t>
+          <t>کارگزاران حمل‌ونقل و بار | اپراتورها و متصدیان نوار نقاله | پیک‌ها و نامه‌رسان‌ها | متصدیان ورود اطلاعات و داده‌آمایی | متصدیان بایگانی و اسناد | کارگران جابه‌جایی دستی بار، کالا و مصالح | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارمندان امور مراسلات و متصدیان ماشین‌های پستی، به جز پست دولتی | متصدیان امور دفتری و امور عمومی اداری | اپراتورهای ماشین‌آلات اداری، به‌جز رایانه | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | کارگران بسته‌بندی دستی | متصدیان باجه و امور پستی | نامه‌رسان‌ها و موزعین پست | مدیران و رؤسای دفاتر پستی | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | کارگران بازیافت و تفکیک پسماند | کارمندان انبار، ارسال و دریافت کالا | متصدیان چیدمان و آماده‌سازی سفارش | متصدیان توزین، سنجش، بازرسی و نمونه‌برداری ثبت اسناد</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | شنیدن فعال | تفکر انتقادی | نگارش | نظارت</t>
+          <t>درک مطلب | سخن گفتن | گوش دادن فعال | تفکر انتقادی | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>تولید و فراوری | خدمات مشتریان و خدمات فردی | زبان انگلیسی | امور اداری و دفتری | مدیریت و امور اداری | رایانه و الکترونیک</t>
+          <t>تولید و فرآوری | خدمات مشتری و شخصی | زبان انگلیسی | اداری | مدیریت و اداره | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | مرتب‌سازی اطلاعات | بیان شفاهی | حساسیت به مسئله | درک کتبی | دید نزدیک | بیان کتبی | استدلال قیاسی | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | وضوح گفتار | سرعت ادراک | استدلال استقرایی</t>
+          <t>درک شفاهی | ترتیب‌دهی اطلاعات | بیان شفاهی | حساسیت به مسئله | درک کتبی | بینایی نزدیک | بیان کتبی | استدلال قیاسی | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | سرعت ادراکی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>متصدیان دیسپاچ و اعزام (به‌جز پلیس، آتش‌نشانی و اورژانس) | سرپرستان رده‌اول کارگران خدماتی و جابه‌جایی دستی مواد | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی مواد | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول کارکنان اداری و پشتیبانی دفتری | سرپرستان رده‌اول کارکنان تولید و عملیات | کاردان‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مدیران تولید صنعتی | کارگران جابه‌جایی دستی بار و اثاثیه | کارشناسان لجستیک | تحلیل‌گران لجستیک | کارمندان امور تدارکات و خرید | کارشناسان مدیریت پروژه | کارمندان ارسال، دریافت و انبارداری | چیدمان‌کنندگان قفسه و آماده‌کنندگان سفارشات | مدیران زنجیره تأمین | مونتاژکاران گروهی خطوط تولید | مدیران حمل‌ونقل، انبارداری و توزیع | توزین‌گران، اندازه‌گیران، کنترل‌کنندگان و نمونه‌برداران ثبت سوابق</t>
+          <t>متصدیان دیسپاچ و اعزام | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده اول کارگران تولید و عملیات | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مدیران تولید صنعتی | کارگران جابه‌جایی دستی بار، کالا و مصالح | کارشناسان لجستیک و مدیریت زنجیره تأمین | تحلیل‌گران لجستیک و فرایند توزیع | کارمندان تدارکات و کارپردازی | کارشناسان مدیریت پروژه | کارمندان انبار، ارسال و دریافت کالا | متصدیان چیدمان و آماده‌سازی سفارش | مدیران زنجیره تامین | مونتاژکاران گروهی | مدیران حمل‌ونقل، انبارداری و توزیع | متصدیان توزین، سنجش، بازرسی و نمونه‌برداری ثبت اسناد</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | شنیدن فعال | نظارت | تفکر انتقادی</t>
+          <t>سخن گفتن | درک مطلب | گوش دادن فعال | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>امور اداری و دفتری | رایانه و الکترونیک | تولید و فراوری | ریاضیات | زبان انگلیسی</t>
+          <t>اداری | رایانه و الکترونیک | تولید و فرآوری | ریاضیات | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>دید نزدیک | بیان شفاهی | حساسیت به مسئله | مرتب‌سازی اطلاعات | درک شفاهی | ثبات دست و بازو | وضوح گفتار | تشخیص گفتار | چابکی دستی | توجه انتخابی | سرعت ادراک | انعطاف‌پذیری در طبقه‌بندی | استدلال استقرایی | استدلال قیاسی | بیان کتبی | درک کتبی</t>
+          <t>بینایی نزدیک | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | درک شفاهی | ثبات دست و بازو | وضوح گفتار | تشخیص گفتار | مهارت دستی | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | بیان کتبی | درک کتبی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>متصدیان باربری و حمل‌ونقل کالا | نامه‌رسان‌ها و پیک‌ها | متصدیان دیسپاچ و اعزام (به‌جز پلیس، آتش‌نشانی و اورژانس) | کارشناسان و متصدیان فورواردری و حمل‌ونقل بین‌المللی کالا | کارگران جابه‌جایی دستی بار و اثاثیه | تحلیل‌گران لجستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات تولیدی | کارمندان پستی و اپراتورهای ماشین‌های تمبر و بسته‌بندی اداری | کارمندان ثبت سفارشات | اپراتورها و مراقبان ماشین‌های بسته‌بندی و پرکن | کارگران بسته‌بندی دستی | متصدیان باجه پست | نامه‌رسان‌های پست | تفکیک‌کنندگان، پردازش‌گران و اپراتورهای دستگاه‌های مرتب‌سازی پست | کارمندان امور تدارکات و خرید | کارمندان برنامه‌ریزی، تولید و پیگیری امور | چیدمان‌کنندگان قفسه و آماده‌کنندگان سفارشات | متصدیان بارگیری مخازن ریلی، تانکرها و شناورها | مدیران حمل‌ونقل، انبارداری و توزیع | توزین‌گران، اندازه‌گیران، کنترل‌کنندگان و نمونه‌برداران ثبت سوابق</t>
+          <t>کارگزاران حمل‌ونقل و بار | پیک‌ها و نامه‌رسان‌ها | متصدیان دیسپاچ و اعزام | کارشناسان و متصدیان فورواردری و حمل‌ونقل بین‌المللی کالا | کارگران جابه‌جایی دستی بار، کالا و مصالح | تحلیل‌گران لجستیک و فرایند توزیع | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارمندان امور مراسلات و متصدیان ماشین‌های پستی، به جز پست دولتی | متصدیان ثبت و پیگیری سفارش‌ها | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | کارگران بسته‌بندی دستی | متصدیان باجه و امور پستی | نامه‌رسان‌ها و موزعین پست | اپراتورها و متصدیان تفکیک و پردازش پستی | کارمندان تدارکات و کارپردازی | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | متصدیان چیدمان و آماده‌سازی سفارش | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی | مدیران حمل‌ونقل، انبارداری و توزیع | متصدیان توزین، سنجش، بازرسی و نمونه‌برداری ثبت اسناد</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
